--- a/selenium-tests/reports/output/Failed_Test_Cases.xlsx
+++ b/selenium-tests/reports/output/Failed_Test_Cases.xlsx
@@ -549,7 +549,7 @@
         <v>Run Date</v>
       </c>
       <c r="B7" t="str">
-        <v>Aug 7, 2026, 9:25 AM</v>
+        <v>Aug 7, 2026, 10:53 AM</v>
       </c>
       <c r="C7" t="str">
         <v/>
